--- a/downloads/indicadores/IMAI/IMAI_datos.xlsx
+++ b/downloads/indicadores/IMAI/IMAI_datos.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf · Fecha de publicación: 11 de agosto de 2026</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_10.pdf · Fecha de publicación: 12 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -10691,7 +10691,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf · Fecha de publicación: 11 de agosto de 2026</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_10.pdf · Fecha de publicación: 12 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -20958,7 +20958,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf · Fecha de publicación: 11 de agosto de 2026</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_10.pdf · Fecha de publicación: 12 de octubre de 2026</t>
         </is>
       </c>
     </row>
